--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88119ED8-D949-4518-909F-9495475741CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF1C982-82D8-4096-8B79-FFCEEEEE6677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t xml:space="preserve">Leetcode </t>
+  </si>
+  <si>
+    <t>Revision Date</t>
   </si>
 </sst>
 </file>
@@ -119,27 +122,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -457,182 +456,223 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5601EDA2-7A16-4CC0-AFDA-1A62F95521CF}">
-  <dimension ref="A3:D24"/>
+  <dimension ref="A3:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="2" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="97.7109375" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.42578125" customWidth="1"/>
+    <col min="4" max="4" width="66.5703125" customWidth="1"/>
+    <col min="5" max="5" width="33.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D5" s="1" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D6" s="1" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D7" s="1" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="5" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:5" s="2" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>1</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="6">
         <v>46181</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="1" t="s">
+      <c r="E11" s="6">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
         <v>2</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="6">
         <v>46182</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="1" t="s">
+      <c r="E13" s="6">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
         <v>3</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="6">
         <v>46183</v>
       </c>
-      <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="9"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="D15" s="4"/>
+      <c r="E15" s="6">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>4</v>
       </c>
-      <c r="B17" s="9">
+      <c r="B17" s="6">
         <v>46184</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="9"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="E17" s="6">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>5</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="6">
         <v>46185</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="E19" s="6">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="E20" s="6"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
         <v>6</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="6">
         <v>46186</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="9"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="E21" s="6">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
         <v>7</v>
       </c>
       <c r="B23" s="6">
         <v>46187</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E23" s="6">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
       <c r="B24" s="6"/>
+      <c r="E24" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="22">
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A3:D4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>

--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF1C982-82D8-4096-8B79-FFCEEEEE6677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF4B0D9-24C8-47F6-A79F-A22B04E057C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -64,6 +64,15 @@
   </si>
   <si>
     <t>Revision Date</t>
+  </si>
+  <si>
+    <t>412. Fizz Buzz</t>
+  </si>
+  <si>
+    <t>9. Palindrome Number</t>
+  </si>
+  <si>
+    <t>C:\Cohort_3.0\DSA\[18] Array-Part-2</t>
   </si>
 </sst>
 </file>
@@ -132,10 +141,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -513,10 +522,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>46181</v>
       </c>
       <c r="C11" t="s">
@@ -525,132 +534,149 @@
       <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>46187</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>10</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>2</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>46182</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="6">
+        <v>14</v>
+      </c>
+      <c r="E13" s="5">
         <v>46188</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="5"/>
       <c r="C14" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>3</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>46183</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="6">
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="5">
         <v>46189</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="5"/>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>4</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>46184</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="5">
         <v>46190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="E18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>5</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>46185</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="5">
         <v>46191</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>6</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>46186</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>46192</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="E22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>7</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>46187</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>46193</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="E24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
@@ -660,11 +686,6 @@
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A17:A18"/>
@@ -672,13 +693,14 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>
     <hyperlink ref="D12" r:id="rId2" xr:uid="{A055ADC4-0C50-4EBB-AAC2-42A8AE638FCD}"/>
-    <hyperlink ref="D13" r:id="rId3" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{03A59C09-BC32-434A-82AE-FA75C0D7F51D}"/>
+    <hyperlink ref="D13" r:id="rId3" xr:uid="{03A59C09-BC32-434A-82AE-FA75C0D7F51D}"/>
     <hyperlink ref="D14" r:id="rId4" xr:uid="{718D8073-FA7F-403D-8032-693A21E24D74}"/>
+    <hyperlink ref="D15" r:id="rId5" xr:uid="{5704977F-AEF4-4952-B5B3-BBE17BE4AC90}"/>
+    <hyperlink ref="D16" r:id="rId6" xr:uid="{41288248-1F9D-4934-98DC-0143D6A88983}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF4B0D9-24C8-47F6-A79F-A22B04E057C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF2C44F-024A-4D23-8687-4AFD814473EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
+    <workbookView xWindow="5100" yWindow="3645" windowWidth="21600" windowHeight="11835" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -144,10 +144,10 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -476,18 +476,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
@@ -522,7 +522,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>1</v>
       </c>
       <c r="B11" s="5">
@@ -539,7 +539,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>10</v>
@@ -550,7 +550,7 @@
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>2</v>
       </c>
       <c r="B13" s="5">
@@ -567,7 +567,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="5"/>
       <c r="C14" t="s">
         <v>10</v>
@@ -575,10 +575,10 @@
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>3</v>
       </c>
       <c r="B15" s="5">
@@ -595,7 +595,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
         <v>10</v>
@@ -606,23 +606,29 @@
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>4</v>
       </c>
       <c r="B17" s="5">
         <v>46184</v>
       </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
       <c r="E17" s="5">
         <v>46190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+      <c r="A18" s="7"/>
       <c r="B18" s="5"/>
-      <c r="E18" s="6"/>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>5</v>
       </c>
       <c r="B19" s="5">
@@ -633,12 +639,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="5"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="7">
         <v>6</v>
       </c>
       <c r="B21" s="5">
@@ -649,12 +655,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="5"/>
-      <c r="E22" s="6"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="7">
         <v>7</v>
       </c>
       <c r="B23" s="5">
@@ -665,18 +671,12 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="5"/>
       <c r="E24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
@@ -693,6 +693,12 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>

--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF2C44F-024A-4D23-8687-4AFD814473EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BFDBAE-237C-42AC-B322-D070850AA390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5100" yWindow="3645" windowWidth="21600" windowHeight="11835" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>C:\Cohort_3.0\DSA\[18] Array-Part-2</t>
+  </si>
+  <si>
+    <t>2665. Counter II</t>
   </si>
 </sst>
 </file>
@@ -144,10 +147,10 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -476,18 +479,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
@@ -522,7 +525,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
       <c r="B11" s="5">
@@ -539,7 +542,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="6"/>
       <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>10</v>
@@ -550,7 +553,7 @@
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>2</v>
       </c>
       <c r="B13" s="5">
@@ -567,7 +570,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="6"/>
       <c r="B14" s="5"/>
       <c r="C14" t="s">
         <v>10</v>
@@ -575,10 +578,10 @@
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>3</v>
       </c>
       <c r="B15" s="5">
@@ -595,7 +598,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="6"/>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
         <v>10</v>
@@ -606,7 +609,7 @@
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>4</v>
       </c>
       <c r="B17" s="5">
@@ -615,20 +618,26 @@
       <c r="C17" t="s">
         <v>11</v>
       </c>
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E17" s="5">
         <v>46190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="6"/>
       <c r="B18" s="5"/>
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>5</v>
       </c>
       <c r="B19" s="5">
@@ -639,12 +648,12 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="6"/>
       <c r="B20" s="5"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>6</v>
       </c>
       <c r="B21" s="5">
@@ -655,12 +664,12 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="5"/>
-      <c r="E22" s="7"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <v>7</v>
       </c>
       <c r="B23" s="5">
@@ -671,12 +680,18 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
+      <c r="A24" s="6"/>
       <c r="B24" s="5"/>
       <c r="E24" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
@@ -693,12 +708,6 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>
@@ -707,6 +716,8 @@
     <hyperlink ref="D14" r:id="rId4" xr:uid="{718D8073-FA7F-403D-8032-693A21E24D74}"/>
     <hyperlink ref="D15" r:id="rId5" xr:uid="{5704977F-AEF4-4952-B5B3-BBE17BE4AC90}"/>
     <hyperlink ref="D16" r:id="rId6" xr:uid="{41288248-1F9D-4934-98DC-0143D6A88983}"/>
+    <hyperlink ref="D17" r:id="rId7" xr:uid="{08609608-82C6-4927-9DC0-51E4DE0C62B1}"/>
+    <hyperlink ref="D18" r:id="rId8" xr:uid="{0AA50DB7-B9C2-4A24-A485-A814F7C56DF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BFDBAE-237C-42AC-B322-D070850AA390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C732360C-D6EE-4CEE-9A76-B0C724265DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="3645" windowWidth="21600" windowHeight="11835" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -57,9 +57,6 @@
     <t>C:\Cohort_3.0\DSA\[17] Array-Part-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheriyans DSA Questions </t>
-  </si>
-  <si>
     <t xml:space="preserve">Leetcode </t>
   </si>
   <si>
@@ -76,6 +73,24 @@
   </si>
   <si>
     <t>2665. Counter II</t>
+  </si>
+  <si>
+    <t>2626. Array Reduce Transformation</t>
+  </si>
+  <si>
+    <t>No Study (College Last Day)</t>
+  </si>
+  <si>
+    <t>2629. Function Composition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheriyans DSA Lecture &amp; Questions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sheriyans DSA Lecture &amp;  Questions </t>
+  </si>
+  <si>
+    <t>2723. Add Two Promises</t>
   </si>
 </sst>
 </file>
@@ -113,12 +128,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -134,7 +155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -147,10 +168,13 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -468,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5601EDA2-7A16-4CC0-AFDA-1A62F95521CF}">
-  <dimension ref="A3:E24"/>
+  <dimension ref="A3:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" style="1" customWidth="1"/>
@@ -479,18 +503,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
@@ -521,18 +545,18 @@
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>1</v>
       </c>
       <c r="B11" s="5">
         <v>46181</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>8</v>
@@ -542,10 +566,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+      <c r="A12" s="7"/>
       <c r="B12" s="5"/>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
@@ -553,145 +577,188 @@
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>2</v>
       </c>
       <c r="B13" s="5">
         <v>46182</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5">
         <v>46188</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
+      <c r="A14" s="7"/>
       <c r="B14" s="5"/>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>3</v>
       </c>
       <c r="B15" s="5">
         <v>46183</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="5">
         <v>46189</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
+      <c r="A16" s="7"/>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>4</v>
       </c>
       <c r="B17" s="5">
         <v>46184</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5">
         <v>46190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
+      <c r="A18" s="7"/>
       <c r="B18" s="5"/>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>5</v>
       </c>
       <c r="B19" s="5">
         <v>46185</v>
       </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="E19" s="5">
         <v>46191</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="6"/>
+      <c r="A20" s="7"/>
       <c r="B20" s="5"/>
+      <c r="C20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="7">
         <v>6</v>
       </c>
       <c r="B21" s="5">
         <v>46186</v>
       </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="E21" s="5">
         <v>46192</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
+      <c r="A22" s="7"/>
       <c r="B22" s="5"/>
-      <c r="E22" s="6"/>
+      <c r="C22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="7">
         <v>7</v>
       </c>
       <c r="B23" s="5">
         <v>46187</v>
       </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="E23" s="5">
         <v>46193</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
+      <c r="A24" s="7"/>
       <c r="B24" s="5"/>
+      <c r="C24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>17</v>
+      </c>
       <c r="E24" s="5"/>
     </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
+  <mergeCells count="25">
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="E25:E26"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
@@ -708,6 +775,12 @@
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>
@@ -718,6 +791,9 @@
     <hyperlink ref="D16" r:id="rId6" xr:uid="{41288248-1F9D-4934-98DC-0143D6A88983}"/>
     <hyperlink ref="D17" r:id="rId7" xr:uid="{08609608-82C6-4927-9DC0-51E4DE0C62B1}"/>
     <hyperlink ref="D18" r:id="rId8" xr:uid="{0AA50DB7-B9C2-4A24-A485-A814F7C56DF2}"/>
+    <hyperlink ref="D19" r:id="rId9" xr:uid="{24EB601B-C326-4956-A118-ABB803620D6E}"/>
+    <hyperlink ref="D21" r:id="rId10" xr:uid="{F618D3BF-E11A-4F24-B38E-6A18EDC38FFF}"/>
+    <hyperlink ref="D23" r:id="rId11" xr:uid="{E1357FA0-85BB-40AA-AE26-E9CF3BEB26EA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DSA/dailyDSA.xlsx
+++ b/DSA/dailyDSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cohort_3.0\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C732360C-D6EE-4CEE-9A76-B0C724265DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2FE577-29F6-4A60-959E-16F0DA2919E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{35766581-4D7B-4E37-938A-384CD03816C5}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="24">
   <si>
     <t>Data Structure and Aligorithm with Java Script</t>
   </si>
@@ -91,6 +91,12 @@
   </si>
   <si>
     <t>2723. Add Two Promises</t>
+  </si>
+  <si>
+    <t>2635. Apply Transform Over Each Element in Array</t>
+  </si>
+  <si>
+    <t>No Study ()</t>
   </si>
 </sst>
 </file>
@@ -165,16 +171,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -503,18 +509,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
@@ -549,10 +555,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="7">
         <v>46181</v>
       </c>
       <c r="C11" t="s">
@@ -561,26 +567,26 @@
       <c r="D11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <v>46187</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
       <c r="C12" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>2</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="7">
         <v>46182</v>
       </c>
       <c r="C13" t="s">
@@ -589,26 +595,26 @@
       <c r="D13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="7">
         <v>46188</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>3</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="7">
         <v>46183</v>
       </c>
       <c r="C15" t="s">
@@ -617,26 +623,26 @@
       <c r="D15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="7">
         <v>46189</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>4</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="7">
         <v>46184</v>
       </c>
       <c r="C17" t="s">
@@ -645,26 +651,26 @@
       <c r="D17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="7">
         <v>46190</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="5"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>5</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="7">
         <v>46185</v>
       </c>
       <c r="C19" t="s">
@@ -673,26 +679,26 @@
       <c r="D19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="7">
         <v>46191</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="8" t="s">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>6</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="7">
         <v>46186</v>
       </c>
       <c r="C21" t="s">
@@ -701,26 +707,26 @@
       <c r="D21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="7">
         <v>46192</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="8" t="s">
+      <c r="A22" s="6"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="7"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <v>7</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="7">
         <v>46187</v>
       </c>
       <c r="C23" t="s">
@@ -729,33 +735,67 @@
       <c r="D23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="7">
         <v>46193</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="8" t="s">
+      <c r="A24" s="6"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="A25" s="6">
+        <v>8</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="7">
+        <v>46194</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="6"/>
       <c r="B26" s="7"/>
+      <c r="C26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="E26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A3:D4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="E19:E20"/>
     <mergeCell ref="A25:A26"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="E25:E26"/>
@@ -763,24 +803,8 @@
     <mergeCell ref="A23:A24"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
     <mergeCell ref="A21:A22"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A3:D4"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D11" r:id="rId1" display="https://leetcode.com/problems/array-prototype-last/" xr:uid="{1436526E-1F16-48F9-AD5C-11C8C12BAA6F}"/>
@@ -794,6 +818,7 @@
     <hyperlink ref="D19" r:id="rId9" xr:uid="{24EB601B-C326-4956-A118-ABB803620D6E}"/>
     <hyperlink ref="D21" r:id="rId10" xr:uid="{F618D3BF-E11A-4F24-B38E-6A18EDC38FFF}"/>
     <hyperlink ref="D23" r:id="rId11" xr:uid="{E1357FA0-85BB-40AA-AE26-E9CF3BEB26EA}"/>
+    <hyperlink ref="D25" r:id="rId12" xr:uid="{8BE3C9FA-D3E2-48E6-B20F-B379AA18CAA9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
